--- a/site/HR-to-Okta-1-1-0-draft/headings.xlsx
+++ b/site/HR-to-Okta-1-1-0-draft/headings.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Prerequisite component</t>
+          <t>Prerequisite Component</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Known Limitations and Issues</t>
+          <t>Known Limitations</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
